--- a/daily_matches/job_matches_2026-05-10.xlsx
+++ b/daily_matches/job_matches_2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior Cloud Software Engineer (Full-Stack)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Anchorage, AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, S3, Kinesis, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa98384834f1f2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software &amp; AI Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Universe Force Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a7cdcfd58fbfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=850bbd121eda6f31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, S3, Docker, Kubernetes, CI/CD, Git, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72936513a7ba9da0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef373ef8fdb9f17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Statistical Modeling &amp; NPW-PTSD Framework Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,46 +587,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75e83c838d157e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e92b0d3de23b3f8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Technical Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PARAMOUNT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Glue, FastAPI, Docker, CI/CD, Terraform, Git, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eda1f03832c35e</t>
+          <t>https://www.indeed.com/viewjob?jk=8797983cc7729f69</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Technical Engineer</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PARAMOUNT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Azure ML, CI/CD, Snowflake, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0be68f0e6578a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bad259f06e93f7fa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Job Title: Senior AI, ML, Cybersecurity &amp; Engineering Talent | Remote | $180K+ Base</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lithium Consulting LLC</t>
+          <t>KlearNow</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,122 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, NLP Engineer, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90f55901056738e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddb293aa1487550</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Insurance Data Analyst</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Orion180 Insurance Services, LLC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a285fb0b75cbb5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Observatory Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brockton, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=191523c6f29afce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Equity Intern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bessemer Trust</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e206bd88f02e0071</t>
         </is>
       </c>
     </row>
